--- a/data/trans_dic/IQ26A_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IQ26A_R2-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,34%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,57%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,71%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,75%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>2,57; 14,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,09</t>
+          <t>3,34; 15,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,14; 15,51</t>
+          <t>0,54; 9,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 14,59</t>
+          <t>0,0; 9,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,38; 16,01</t>
+          <t>1,04; 9,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 9,87</t>
+          <t>4,06; 15,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 28,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,98</t>
+          <t>1,97; 8,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 10,46</t>
+          <t>3,24; 10,64</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 10,66</t>
+          <t>3,16; 10,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,4</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>13,72%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>17,83%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>27,63%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 19,63</t>
+          <t>4,75; 12,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,1; 24,17</t>
+          <t>9,12; 19,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,34; 35,67</t>
+          <t>20,01; 33,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 30,07</t>
+          <t>0,0; 16,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,2; 13,49</t>
+          <t>8,74; 19,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 19,96</t>
+          <t>12,28; 24,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 33,4</t>
+          <t>20,52; 34,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,12</t>
+          <t>3,77; 28,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,28</t>
+          <t>7,62; 14,42</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11,8; 19,96</t>
+          <t>12,22; 20,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,09; 32,61</t>
+          <t>22,19; 31,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 14,87</t>
+          <t>3,03; 16,43</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17,75%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>17,86%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,17%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,75%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17,8%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,09; 26,6</t>
+          <t>11,61; 26,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,59</t>
+          <t>0,95; 8,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 26,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,64; 25,85</t>
+          <t>10,33; 26,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 7,85</t>
+          <t>0,0; 7,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
+          <t>3,43; 28,28</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12,43; 23,04</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0,99; 5,72</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>12,77; 23,48</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0,57; 5,54</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 15,27</t>
+          <t>1,94; 15,65</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22,43%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24,09%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>44,72%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>10,85%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>16,11%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,99%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,1; 19,09</t>
+          <t>4,57; 15,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 22,42</t>
+          <t>15,17; 31,7</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,03; 24,17</t>
+          <t>16,37; 32,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 55,76</t>
+          <t>11,9; 77,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 16,03</t>
+          <t>6,08; 18,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,14; 30,68</t>
+          <t>8,39; 21,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,56; 33,91</t>
+          <t>10,21; 23,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 71,71</t>
+          <t>9,12; 55,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 14,29</t>
+          <t>6,29; 14,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,79; 24,5</t>
+          <t>13,95; 24,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,59; 26,42</t>
+          <t>14,87; 26,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,12; 55,4</t>
+          <t>17,73; 58,07</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>62,59%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,27%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>80,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,61</t>
+          <t>0,0; 9,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 20,67</t>
+          <t>4,41; 19,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58,88; 94,66</t>
+          <t>41,44; 83,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,31</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 19,58</t>
+          <t>4,72; 20,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 16,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>37,86; 81,26</t>
+          <t>56,45; 94,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,08</t>
+          <t>0,83; 7,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 16,9</t>
+          <t>5,61; 16,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,34</t>
+          <t>0,0; 7,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,34; 83,84</t>
+          <t>55,51; 84,14</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7,37%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>16,85%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4,19%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,67%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9,52; 25,63</t>
+          <t>3,18; 14,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 10,76</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,79</t>
+          <t>1,27; 11,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,05</t>
+          <t>0,0; 17,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,59</t>
+          <t>9,7; 26,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>1,36; 11,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,0</t>
+          <t>1,27; 11,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,84</t>
+          <t>0,0; 32,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,97; 17,46</t>
+          <t>7,93; 17,48</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,31</t>
+          <t>0,7; 6,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 8,32</t>
+          <t>1,46; 8,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,47</t>
+          <t>0,0; 15,55</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24,95%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44,69%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>14,44%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>5,39%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>27,55%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>56,41%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,81; 19,51</t>
+          <t>10,1; 21,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,87</t>
+          <t>1,97; 8,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21,54; 34,15</t>
+          <t>19,13; 30,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40,24; 73,0</t>
+          <t>28,94; 59,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,18; 21,04</t>
+          <t>10,14; 20,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 8,26</t>
+          <t>2,72; 9,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,74; 30,9</t>
+          <t>21,76; 34,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,65; 62,93</t>
+          <t>36,64; 67,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,44; 18,35</t>
+          <t>11,0; 18,26</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 7,26</t>
+          <t>2,9; 7,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21,95; 30,99</t>
+          <t>22,51; 30,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,97; 61,26</t>
+          <t>36,81; 58,11</t>
         </is>
       </c>
     </row>
@@ -1629,44 +1629,44 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>17,88%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>17,48%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>16,32%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>8,46%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>17,88%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4,42%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>17,69%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,02; 22,48</t>
+          <t>13,4; 23,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11,91; 21,61</t>
+          <t>13,05; 22,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,63; 12,51</t>
+          <t>7,61; 15,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
+          <t>0,0; 14,91</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,42; 23,14</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>11,98; 21,75</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,35; 12,11</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>13,75; 23,17</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>13,05; 22,16</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,42; 15,72</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,53</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14,57; 21,43</t>
+          <t>14,66; 21,04</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,81; 20,6</t>
+          <t>13,59; 20,38</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 12,84</t>
+          <t>7,48; 12,81</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,16</t>
+          <t>0,0; 9,62</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11,38; 15,74</t>
+          <t>10,22; 14,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,63; 12,63</t>
+          <t>9,15; 13,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,86</t>
+          <t>12,32; 16,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18,56; 31,16</t>
+          <t>13,88; 23,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,29</t>
+          <t>11,84; 15,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,27; 13,11</t>
+          <t>8,67; 12,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,47; 16,98</t>
+          <t>12,71; 16,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13,39; 23,93</t>
+          <t>18,13; 30,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11,49; 14,39</t>
+          <t>11,28; 14,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9,46; 12,22</t>
+          <t>9,43; 12,12</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13,05; 16,08</t>
+          <t>13,03; 16,25</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,0; 25,21</t>
+          <t>17,03; 25,11</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2350</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1281</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2113</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4933</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3750</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5176</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2350</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>589</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>589</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4549</t>
+          <t>1475; 8283</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>517; 4607</t>
+          <t>2070; 9750</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2332; 8741</t>
+          <t>347; 6425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3184</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1360; 8383</t>
+          <t>0; 4565</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2099; 9937</t>
+          <t>592; 5236</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>591; 6361</t>
+          <t>2290; 8875</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3584</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2031; 9636</t>
+          <t>2116; 9388</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3762; 12442</t>
+          <t>3856; 12660</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3847; 12883</t>
+          <t>3814; 13097</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 2862</t>
+          <t>0; 3231</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8674</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14343</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28413</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1199</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13340</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>17951</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28080</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2754</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8674</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14343</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28413</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3850</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8749; 19093</t>
+          <t>5134; 13698</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12182; 24331</t>
+          <t>9548; 20531</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20675; 36253</t>
+          <t>21668; 36679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>918; 6906</t>
+          <t>0; 4734</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4543; 14585</t>
+          <t>8504; 19412</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9194; 20893</t>
+          <t>12366; 24543</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20544; 36174</t>
+          <t>20855; 35081</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5237</t>
+          <t>764; 5842</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15022; 29316</t>
+          <t>15643; 29619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24236; 40989</t>
+          <t>25094; 42666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46375; 68467</t>
+          <t>46576; 66683</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1683; 8249</t>
+          <t>1490; 8077</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,62 +2557,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12367</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>11941</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1420</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2114</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12367</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>24308</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3454</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>24308</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3454</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2041</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7417; 17786</t>
+          <t>8088; 18515</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>647; 5495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>659; 4928</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8111; 18016</t>
+          <t>6911; 17997</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>641; 5377</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,27 +2660,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>641; 5293</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>16980; 31464</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1326; 7653</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>17445; 32070</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>770; 7421</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>642; 5294</t>
+          <t>639; 5141</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>7060</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>18152</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>19558</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4730</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>7829</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>10682</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>12309</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4042</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>7060</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>18152</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19558</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8245</t>
+          <t>8614</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4402; 13771</t>
+          <t>3588; 12130</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6162; 16716</t>
+          <t>12278; 25651</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7664; 18474</t>
+          <t>13287; 26755</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1416; 7714</t>
+          <t>1258; 8224</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3621; 12582</t>
+          <t>4386; 13664</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12250; 24822</t>
+          <t>6254; 16204</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13446; 27532</t>
+          <t>7803; 18200</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1067; 7773</t>
+          <t>1308; 8023</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9766; 21520</t>
+          <t>9474; 21856</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21435; 38094</t>
+          <t>21685; 38094</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24568; 41642</t>
+          <t>23437; 41188</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4225; 13667</t>
+          <t>4418; 14472</t>
         </is>
       </c>
     </row>
@@ -2910,37 +2910,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4780</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6912</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1345</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>4510</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2116</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8224</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1391</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4780</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>15454</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4708</t>
+          <t>0; 4229</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1663; 9072</t>
+          <t>2030; 9093</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 7051</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6052; 9732</t>
+          <t>4576; 9270</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4555</t>
+          <t>0; 4585</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2035; 9022</t>
+          <t>2070; 9030</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6970</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4027; 8643</t>
+          <t>6022; 10113</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>701; 6844</t>
+          <t>701; 6146</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5434; 15202</t>
+          <t>5050; 14776</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 7375</t>
+          <t>0; 6382</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11575; 17536</t>
+          <t>12054; 18268</t>
         </is>
       </c>
     </row>
@@ -3113,37 +3113,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>4358</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2378</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>9324</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2208</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2159</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4358</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>787</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2378</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>679</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1199</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5269; 14178</t>
+          <t>1878; 8757</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>709; 5673</t>
+          <t>0; 3968</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>673; 5788</t>
+          <t>732; 6894</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3201</t>
+          <t>0; 2715</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1860; 8034</t>
+          <t>5366; 14729</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3875</t>
+          <t>715; 6322</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>755; 6928</t>
+          <t>681; 6092</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 2544</t>
+          <t>0; 2887</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9123; 19980</t>
+          <t>9070; 20005</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>777; 6901</t>
+          <t>768; 7018</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2041; 9264</t>
+          <t>1624; 9039</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3946</t>
+          <t>0; 3850</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>19639</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5919</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>35637</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>18055</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>18480</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>7197</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>37500</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>15930</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>19639</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5919</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>35637</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>14125</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>32181</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>12550; 24958</t>
+          <t>13384; 28053</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3517; 13193</t>
+          <t>2721; 11109</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29315; 46477</t>
+          <t>27324; 44153</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11365; 20615</t>
+          <t>11693; 23936</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>13499; 27888</t>
+          <t>12981; 26045</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3176; 11393</t>
+          <t>3635; 12580</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26769; 44141</t>
+          <t>29612; 46709</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13892; 26776</t>
+          <t>9892; 18234</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>29795; 47810</t>
+          <t>28654; 47563</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8182; 19702</t>
+          <t>7873; 19056</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61232; 86438</t>
+          <t>62791; 84865</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>28294; 43369</t>
+          <t>24809; 39163</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,44 +3597,44 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>28888</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>28916</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>18661</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>27178</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>26189</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>13709</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>28888</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>28916</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>18661</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
           <t>56067</t>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1871</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>20244; 34957</t>
+          <t>21647; 38337</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>19114; 34673</t>
+          <t>21745; 37523</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>9125; 20268</t>
+          <t>12777; 26521</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>0; 5884</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>20865; 35975</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>19224; 34904</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>8674; 19620</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>22212; 37424</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>21737; 36915</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>12463; 26402</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>0; 5678</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>46174; 67948</t>
+          <t>46461; 66691</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>45160; 67369</t>
+          <t>44456; 66655</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>24632; 42385</t>
+          <t>24688; 42264</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 5904</t>
+          <t>0; 6281</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>86126</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>80108</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>106996</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>33286</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>90719</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>72270</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>100807</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>34308</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>86126</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>80108</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>106996</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>68395</t>
+          <t>65798</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>75760; 104758</t>
+          <t>72698; 102824</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>59395; 86929</t>
+          <t>66216; 94161</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87132; 116586</t>
+          <t>90733; 122750</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26286; 44143</t>
+          <t>24706; 42485</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>72335; 101655</t>
+          <t>78806; 105613</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>67074; 94857</t>
+          <t>59649; 86380</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91825; 125082</t>
+          <t>87884; 117410</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>25523; 45615</t>
+          <t>25021; 42385</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>158159; 198043</t>
+          <t>155289; 197327</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>133547; 172507</t>
+          <t>133112; 171127</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>186417; 229676</t>
+          <t>186116; 232128</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>56479; 83764</t>
+          <t>53818; 79361</t>
         </is>
       </c>
     </row>
